--- a/artfynd/A 11516-2026 artfynd.xlsx
+++ b/artfynd/A 11516-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131728797</v>
       </c>
       <c r="B2" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131728150</v>
       </c>
       <c r="B3" t="n">
-        <v>97899</v>
+        <v>97900</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>131728867</v>
       </c>
       <c r="B4" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>131727420</v>
       </c>
       <c r="B5" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 11516-2026 artfynd.xlsx
+++ b/artfynd/A 11516-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131728797</v>
       </c>
       <c r="B2" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131728150</v>
       </c>
       <c r="B3" t="n">
-        <v>97900</v>
+        <v>97903</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>131728867</v>
       </c>
       <c r="B4" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>131727420</v>
       </c>
       <c r="B5" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 11516-2026 artfynd.xlsx
+++ b/artfynd/A 11516-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131728797</v>
       </c>
       <c r="B2" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131728150</v>
       </c>
       <c r="B3" t="n">
-        <v>97903</v>
+        <v>97909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>131728867</v>
       </c>
       <c r="B4" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>131727420</v>
       </c>
       <c r="B5" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 11516-2026 artfynd.xlsx
+++ b/artfynd/A 11516-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131728797</v>
       </c>
       <c r="B2" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131728150</v>
       </c>
       <c r="B3" t="n">
-        <v>97909</v>
+        <v>97912</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>131728867</v>
       </c>
       <c r="B4" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>131727420</v>
       </c>
       <c r="B5" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 11516-2026 artfynd.xlsx
+++ b/artfynd/A 11516-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131728797</v>
       </c>
       <c r="B2" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131728150</v>
       </c>
       <c r="B3" t="n">
-        <v>97912</v>
+        <v>97917</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>131728867</v>
       </c>
       <c r="B4" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>131727420</v>
       </c>
       <c r="B5" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 11516-2026 artfynd.xlsx
+++ b/artfynd/A 11516-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131728797</v>
       </c>
       <c r="B2" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131728150</v>
       </c>
       <c r="B3" t="n">
-        <v>97917</v>
+        <v>97919</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>131728867</v>
       </c>
       <c r="B4" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>131727420</v>
       </c>
       <c r="B5" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 11516-2026 artfynd.xlsx
+++ b/artfynd/A 11516-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>131728150</v>
       </c>
       <c r="B3" t="n">
-        <v>97960</v>
+        <v>97963</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11516-2026 artfynd.xlsx
+++ b/artfynd/A 11516-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131728797</v>
+        <v>131727420</v>
       </c>
       <c r="B2" t="n">
-        <v>57945</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>330893</v>
+        <v>330837</v>
       </c>
       <c r="R2" t="n">
-        <v>6430685</v>
+        <v>6430599</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131728150</v>
+        <v>131728797</v>
       </c>
       <c r="B3" t="n">
-        <v>97963</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,36 +798,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -836,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>330879</v>
+        <v>330893</v>
       </c>
       <c r="R3" t="n">
-        <v>6430625</v>
+        <v>6430685</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,11 +902,11 @@
         <v>131728867</v>
       </c>
       <c r="B4" t="n">
-        <v>57945</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1020,27 +1011,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131727420</v>
+        <v>131727574</v>
       </c>
       <c r="B5" t="n">
-        <v>57945</v>
+        <v>58131</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103023</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1048,10 +1039,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1066,7 +1061,7 @@
         <v>6430599</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,6 +1124,243 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131728713</v>
+      </c>
+      <c r="B6" t="n">
+        <v>111181</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221037</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vildkaprifol</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lonicera periclymenum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Strömmalyckan, Strömmalyckan, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>330871</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6430634</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131728150</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Strömmalyckan, Strömmalyckan, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>330879</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6430625</v>
+      </c>
+      <c r="S7" t="n">
+        <v>7</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11516-2026 artfynd.xlsx
+++ b/artfynd/A 11516-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131727420</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728797</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728867</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,6 +1144,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131727574</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1240,6 +1265,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728713</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1361,8 +1391,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131728150</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>